--- a/Valuaciones_USA/CI_valuaciones_hits_por_anio.xlsx
+++ b/Valuaciones_USA/CI_valuaciones_hits_por_anio.xlsx
@@ -860,16 +860,10 @@
         <v>23</v>
       </c>
       <c r="C19">
-        <v>72.06</v>
+        <v>57.06</v>
       </c>
       <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
-      </c>
-      <c r="F19" s="2">
-        <v>41673</v>
+        <v>0</v>
       </c>
       <c r="G19" t="s">
         <v>26</v>
@@ -929,7 +923,7 @@
         <v>23</v>
       </c>
       <c r="C22">
-        <v>116.9</v>
+        <v>121.25</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
